--- a/AAII_Financials/Quarterly/SWAV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SWAV_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="92">
   <si>
     <t>SWAV</t>
   </si>
@@ -656,327 +656,339 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>203000</v>
+      </c>
+      <c r="E8" s="3">
         <v>186000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>180200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>161100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>144000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>131300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>120700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>93600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>84200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>65200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>55900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>31900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>22700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>19600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>15200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>14300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>24500</v>
+        <v>25300</v>
       </c>
       <c r="E9" s="3">
         <v>24500</v>
       </c>
       <c r="F9" s="3">
+        <v>24500</v>
+      </c>
+      <c r="G9" s="3">
         <v>21100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>17500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>17900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>16700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>177700</v>
+      </c>
+      <c r="E10" s="3">
         <v>161500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>155700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>140000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>126500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>113400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>104000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>80700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>71500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>54300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>46000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>24000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>16200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>14300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>9500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>8700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>6900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,79 +1014,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E12" s="3">
         <v>39500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>36800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>27000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>23700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>20200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>20800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>17000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>14700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>13700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>11800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>10300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>9000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>7900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>8100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>11900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>10100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>8400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>6900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>7500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>6100</v>
-      </c>
-      <c r="X12" s="3">
-        <v>5500</v>
       </c>
       <c r="Y12" s="3">
         <v>5500</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,17 +1160,20 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>700</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1170,8 +1189,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1215,8 +1234,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1286,8 +1308,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1335,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>159700</v>
+      </c>
+      <c r="E17" s="3">
         <v>143100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>147800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>121300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>101600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>94600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>91200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>78300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>70200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>62300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>56100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>49400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>38600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>32400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>28300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>34200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>29700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>24400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>21300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>19400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>16200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>13700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>43300</v>
+      </c>
+      <c r="E18" s="3">
         <v>42900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>32400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>39800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>42400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>36700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>29500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>15300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>14000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-17500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-15900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-12800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-18000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-19000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-15400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-13100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-11300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-12100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-11100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-10100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-9800</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,167 +1511,174 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E20" s="3">
         <v>4000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-700</v>
       </c>
       <c r="L20" s="3">
         <v>-700</v>
       </c>
       <c r="M20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
-      </c>
-      <c r="P20" s="3">
-        <v>200</v>
       </c>
       <c r="Q20" s="3">
         <v>200</v>
       </c>
       <c r="R20" s="3">
+        <v>200</v>
+      </c>
+      <c r="S20" s="3">
         <v>500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-400</v>
-      </c>
-      <c r="W20" s="3">
-        <v>100</v>
       </c>
       <c r="X20" s="3">
         <v>100</v>
       </c>
       <c r="Y20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z20" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>61500</v>
+      </c>
+      <c r="E21" s="3">
         <v>49900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>36400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>43100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>47200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>36700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>27700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>16000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>14200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-22500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-15100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-17300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-18000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-14100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-12300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-10100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-12300</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>300</v>
       </c>
       <c r="I22" s="3">
         <v>300</v>
@@ -1651,10 +1690,10 @@
         <v>300</v>
       </c>
       <c r="L22" s="3">
+        <v>300</v>
+      </c>
+      <c r="M22" s="3">
         <v>200</v>
-      </c>
-      <c r="M22" s="3">
-        <v>300</v>
       </c>
       <c r="N22" s="3">
         <v>300</v>
@@ -1672,16 +1711,16 @@
         <v>300</v>
       </c>
       <c r="S22" s="3">
+        <v>300</v>
+      </c>
+      <c r="T22" s="3">
         <v>200</v>
-      </c>
-      <c r="T22" s="3">
-        <v>300</v>
       </c>
       <c r="U22" s="3">
         <v>300</v>
       </c>
       <c r="V22" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W22" s="3">
         <v>200</v>
@@ -1690,107 +1729,113 @@
         <v>200</v>
       </c>
       <c r="Y22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>55500</v>
+      </c>
+      <c r="E23" s="3">
         <v>45100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>33000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>40700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>44700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>35100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>26300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>14700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>13000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-23600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-15900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-18100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-18800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-14700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-12900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-10600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-12800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-11200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E24" s="3">
         <v>10100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-96300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
-      </c>
-      <c r="K24" s="3">
-        <v>100</v>
       </c>
       <c r="L24" s="3">
         <v>100</v>
@@ -1799,7 +1844,7 @@
         <v>100</v>
       </c>
       <c r="N24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -1834,8 +1879,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>44300</v>
+      </c>
+      <c r="E26" s="3">
         <v>35000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>28900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>39100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>140900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>35000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>25600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>14500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>12900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-23600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-15900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-18100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-18800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-14700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-13000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-10600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-12800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-11200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>44300</v>
+      </c>
+      <c r="E27" s="3">
         <v>35000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>28900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>39100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>140900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>35000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>25600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>14500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>12900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-23600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-15900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-18100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-18800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-14700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-13000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-10600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-12800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-11200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2249,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,150 +2397,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>700</v>
       </c>
       <c r="L32" s="3">
         <v>700</v>
       </c>
       <c r="M32" s="3">
+        <v>700</v>
+      </c>
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-200</v>
       </c>
       <c r="Q32" s="3">
         <v>-200</v>
       </c>
       <c r="R32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S32" s="3">
         <v>-500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>400</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-100</v>
       </c>
       <c r="X32" s="3">
         <v>-100</v>
       </c>
       <c r="Y32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>44300</v>
+      </c>
+      <c r="E33" s="3">
         <v>35000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>28900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>39100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>140900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>35000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>25600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>14500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>12900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-23600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-15900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-18100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-18800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-14700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-13000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-10600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-12800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-11200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>44300</v>
+      </c>
+      <c r="E35" s="3">
         <v>35000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>28900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>39100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>140900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>35000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>25600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>14500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>12900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-23600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-15900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-18100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-18800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-14700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-13000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-10600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-12800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-11200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,139 +2830,143 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>328400</v>
+      </c>
+      <c r="E41" s="3">
         <v>498100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>141500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>280900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>156600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>127800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>99900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>66300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>89200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>91200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>84300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>57000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>50400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>215300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>218300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>123100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>139000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>39500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>41900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>138100</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>662100</v>
+      </c>
+      <c r="E42" s="3">
         <v>419200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>117100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>135900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>147900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>122900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>125000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>134900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>111800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>91800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>90500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>120400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>151900</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q42" s="3">
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3">
         <v>13100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>47300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>56300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>74600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>83200</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2887,330 +2976,345 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>114600</v>
+      </c>
+      <c r="E43" s="3">
         <v>98800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>96600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>84300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>71400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>64200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>59800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>47800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>37400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>30000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>25000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>19600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>11700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3900</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>107600</v>
+      </c>
+      <c r="E44" s="3">
         <v>97200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>92100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>83300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>75100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>69000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>60000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>53400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>43000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>38700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>36100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>33500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>29900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>28900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>23400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>15900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>12100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>9200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>8300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>7000</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E45" s="3">
         <v>15200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2500</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1225300</v>
+      </c>
+      <c r="E46" s="3">
         <v>1128500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>456400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>590800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>459300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>395300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>352000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>309900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>285900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>256000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>239600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>233100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>246300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>257900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>264300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>197600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>216700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>131100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>140600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>151500</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E47" s="3">
         <v>1800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6400</v>
-      </c>
-      <c r="M47" s="3">
-        <v>6800</v>
       </c>
       <c r="N47" s="3">
         <v>6800</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
+      <c r="O47" s="3">
+        <v>6800</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
@@ -3227,8 +3331,8 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -3242,91 +3346,97 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>98600</v>
+      </c>
+      <c r="E48" s="3">
         <v>92400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>90900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>85700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>80500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>72400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>58300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>54600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>51900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>34900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>28300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>27400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>23900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5400</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>132400</v>
+      </c>
+      <c r="E49" s="3">
         <v>133600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>134500</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3342,8 +3452,8 @@
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="L49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -3384,8 +3494,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,79 +3642,85 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>108600</v>
+      </c>
+      <c r="E52" s="3">
         <v>117700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>102300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>104100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>102800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1900</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1700</v>
       </c>
       <c r="M52" s="3">
         <v>1700</v>
       </c>
       <c r="N52" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="O52" s="3">
         <v>1800</v>
       </c>
       <c r="P52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q52" s="3">
         <v>1700</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>1600</v>
       </c>
       <c r="R52" s="3">
         <v>1600</v>
       </c>
       <c r="S52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="T52" s="3">
         <v>1500</v>
-      </c>
-      <c r="T52" s="3">
-        <v>500</v>
       </c>
       <c r="U52" s="3">
         <v>500</v>
       </c>
       <c r="V52" s="3">
+        <v>500</v>
+      </c>
+      <c r="W52" s="3">
         <v>600</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3790,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1566600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1474000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>786600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>783200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>646100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>475800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>417100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>372500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>345700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>299000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>276400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>269100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>272000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>280700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>287400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>220700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>231900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>137900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>146800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>157500</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,79 +3922,83 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E57" s="3">
         <v>6900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4000</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3875,352 +4008,367 @@
       <c r="E58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F58" s="3">
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3">
         <v>80000</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>11000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1700</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
       <c r="S58" s="3">
-        <v>6700</v>
+        <v>0</v>
       </c>
       <c r="T58" s="3">
         <v>6700</v>
       </c>
       <c r="U58" s="3">
+        <v>6700</v>
+      </c>
+      <c r="V58" s="3">
         <v>5000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3300</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>95300</v>
+      </c>
+      <c r="E59" s="3">
         <v>71300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>67400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>50900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>56700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>50800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>49900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>34300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>42600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>33900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>29200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>24800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>20800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>16600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>14600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>10200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7300</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>104200</v>
+      </c>
+      <c r="E60" s="3">
         <v>78200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>80200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>142000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>63400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>54200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>66200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>51000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>51600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>40300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>36000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>33500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>25600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>21100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>17700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>18800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>24000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>19400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>15400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>14600</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>731900</v>
+      </c>
+      <c r="E61" s="3">
         <v>730900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>24300</v>
-      </c>
-      <c r="F61" s="3">
-        <v>24200</v>
       </c>
       <c r="G61" s="3">
         <v>24200</v>
       </c>
       <c r="H61" s="3">
+        <v>24200</v>
+      </c>
+      <c r="I61" s="3">
         <v>14900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>12800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>14800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>16300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>16100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>10300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>11800</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>61800</v>
+      </c>
+      <c r="E62" s="3">
         <v>63600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>65200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>46300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>47200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>50800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>39400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>44600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>40600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>24200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>19200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>19500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7900</v>
-      </c>
-      <c r="R62" s="3">
-        <v>8100</v>
       </c>
       <c r="S62" s="3">
         <v>8100</v>
       </c>
       <c r="T62" s="3">
+        <v>8100</v>
+      </c>
+      <c r="U62" s="3">
         <v>1500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1900</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,79 +4586,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>897900</v>
+      </c>
+      <c r="E66" s="3">
         <v>872700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>169700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>212600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>134800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>119900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>112100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>104700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>103900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>78700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>68000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>64800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>46400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>43600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>41900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>43000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>39300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>29600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>27400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>28400</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,79 +4984,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>110500</v>
+      </c>
+      <c r="E72" s="3">
         <v>66200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>31200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-36800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-177700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-212700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-238300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-252800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-265800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-267700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-267300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-243700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-227800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-214900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-196700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-178000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-163200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-150300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-139700</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5280,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>668700</v>
+      </c>
+      <c r="E76" s="3">
         <v>601200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>616900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>570700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>511300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>355900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>305100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>267800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>241800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>220300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>208300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>204300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>225700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>237000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>245400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>177800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>192700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>108300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>119400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>129200</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>44300</v>
+      </c>
+      <c r="E81" s="3">
         <v>35000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>28900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>39100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>140900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>35000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>25600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>14500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>12900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-23600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-15900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-18100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-18800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-14700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-13000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-10600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-12800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-11200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,46 +5611,47 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E83" s="3">
         <v>3000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>700</v>
-      </c>
-      <c r="O83" s="3">
-        <v>500</v>
       </c>
       <c r="P83" s="3">
         <v>500</v>
@@ -5462,13 +5660,13 @@
         <v>500</v>
       </c>
       <c r="R83" s="3">
+        <v>500</v>
+      </c>
+      <c r="S83" s="3">
         <v>400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>500</v>
-      </c>
-      <c r="T83" s="3">
-        <v>300</v>
       </c>
       <c r="U83" s="3">
         <v>300</v>
@@ -5476,17 +5674,20 @@
       <c r="V83" s="3">
         <v>300</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X83" s="3">
+      <c r="W83" s="3">
+        <v>300</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y83" s="3">
         <v>200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6053,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>71700</v>
+      </c>
+      <c r="E89" s="3">
         <v>50700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>39700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>34000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>52400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>34500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>28900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>20800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>9300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-17300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-12400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-18200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-24200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-12600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-10600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-10500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-14400</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X89" s="3">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-11400</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,79 +6157,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-400</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-300</v>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y91" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,79 +6377,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-242300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-305900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-83800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>6200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-35300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>5800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-27400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-23100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>27200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>27100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-153600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>12100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>29700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>4300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>16800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>7600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-83600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-400</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X94" s="3">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6481,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6320,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,100 +6775,106 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E100" s="3">
         <v>613000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-95800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>83400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>9600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>83600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>96400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>113300</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
+      <c r="X100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1200</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6642,8 +6890,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -6675,75 +6923,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-169600</v>
+      </c>
+      <c r="E102" s="3">
         <v>357000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-140200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>124300</v>
-      </c>
-      <c r="G102" s="3">
-        <v>28400</v>
       </c>
       <c r="H102" s="3">
         <v>28400</v>
       </c>
       <c r="I102" s="3">
+        <v>28400</v>
+      </c>
+      <c r="J102" s="3">
         <v>33700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-23000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>27300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-164800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>95200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-15900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>100600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-96100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>98400</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-9500</v>
       </c>
     </row>
